--- a/content/tz-drug-na-kitayskom.xlsx
+++ b/content/tz-drug-na-kitayskom.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -667,46 +667,58 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Целевой объём блока T123</t>
+          <t>Объём блока T123</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>38 000–43 000 (лимит ≈ 50 000). Вилка поднята сознательно: в прошлой статье план 37 000–40 000 оказался нереалистичным, факт 44 901</t>
+          <t>ПЛАН 38 000–43 000. ФАКТ 44 128 — на 1 128 выше вилки, лимит 50 000 не нарушен</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция инфографики</t>
+          <t>Позиция инфографики</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>26–31 %</t>
+          <t>ПЛАН 26–31 %. ФАКТ 27,0 %</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Целевая позиция «Из личного опыта»</t>
+          <t>Позиция «Из личного опыта»</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>36–40 %</t>
+          <t>ПЛАН 36–40 %. ФАКТ 36,7 % — после перестановки разделов 3 и 4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Позиция FAQ</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>77,1 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Ключи и где отрабатываются</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>как будет друг на китайском — тайтл, H1, первый абзац, раздел 1, FAQ. друг перевод на китайский — раздел 1, сводная таблица семи слов, FAQ. друзья на китайском — H2 раздела про 们, подпись инфографики, FAQ. друзья по-китайски — раздел про 们, FAQ. ВАЖНО: два ключа из четырёх — про множественное число, и бриф их никак не отрабатывает</t>
         </is>
@@ -728,7 +740,7 @@
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -766,7 +778,11 @@
           <t>38 000–43 000, лимит ≈ 50 000</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>44 128 — НА 1 128 ВЫШЕ ВИЛКИ, лимит не нарушен, запас ≈ 5 800</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -779,7 +795,11 @@
           <t>26–31 %</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>27,0 %</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -792,7 +812,11 @@
           <t>36–40 %</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>36,7 % — после перестановки разделов 3 и 4; до перестановки было 48,5 %</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -805,7 +829,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>77,1 %</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -818,7 +846,11 @@
           <t>A = B</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>22 / 22</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -831,7 +863,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -844,7 +880,11 @@
           <t>position: sticky, top 90</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>sticky, top 90px</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -857,7 +897,11 @@
           <t>static, order 2, нет горизонтальной прокрутки</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>static, order 2, ширина документа 390</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -870,7 +914,11 @@
           <t>да</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>да: BlogPosting, Person, EducationalOrganization, FAQPage, BreadcrumbList</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -883,7 +931,11 @@
           <t>совпадение полное</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>6 вопросов и 6 ответов, совпадение полное</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -896,7 +948,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>0; ёлочек 41 пара</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -909,7 +965,11 @@
           <t>все верны</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>найдена и исправлена одна: «про корректировка произношения» → «про корректировку произношения»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -922,7 +982,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>найдена и исправлена одна: «спотыкается иностранец» → «ошибается иностранец»</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -935,7 +999,11 @@
           <t>запрещён</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>ПРАВИЛА .han В УНАСЛЕДОВАННОМ CSS НЕ БЫЛО ВООБЩЕ — разметка ничего не делала. Добавлено #ks-art .han с шрифтом и white-space: nowrap. То же касается предыдущей статьи про поступление после 11 класса</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -948,7 +1016,11 @@
           <t>подбирается замером</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>452 px при содержимом до 428, запас 24</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -961,7 +1033,11 @@
           <t>0 на отдаче</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>найдено и исправлено шесть, перечислены на листе Картинки</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -974,7 +1050,11 @@
           <t>7 в исходнике / 5 в блоке, assets = 0</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>ждём ссылки от заказчика</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1566,12 +1646,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>哥们儿 и 兄弟: слова мужской компании</t>
+          <t>闺蜜, 发小 и 知己: когда нужно сказать больше</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>регистр, север и эризация, почему их не говорят начальнику</t>
+          <t>ПЕРЕСТАВЛЕН С 4-го МЕСТА. Женская дружба, друг детства, книжный край. ЗДЕСЬ «ИЗ ЛИЧНОГО ОПЫТА»</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1661,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>闺蜜, 发小 и 知己: когда нужно сказать больше</t>
+          <t>哥们儿 и 兄弟: слова мужской компании</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>женская дружба, друг детства, книжный край. ЗДЕСЬ «ИЗ ЛИЧНОГО ОПЫТА»</t>
+          <t>ПЕРЕСТАВЛЕН С 3-го МЕСТА. Регистр, север и эризация, почему их не говорят начальнику. Причина перестановки: история стояла на 48,5 %, далеко за нормой. Заодно статья стала логичнее — сначала ось близости, потом ось речи, ровно как на инфографике</t>
         </is>
       </c>
     </row>
@@ -1937,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2070,13 +2150,102 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Дефекты рендеров</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr"/>
+          <t>ДЕФЕКТ 1. Обложка</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>между пиньинем и пометой зиял провал шириной около трети карточки</t>
+        </is>
+      </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>проставляется после просмотра</t>
+          <t>добавлена колонка с русским переводом каждого слова — и пустота ушла, и картинка стала полезнее</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 2. Инфографика</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>КАРТОЧКА 发小 ЛЕЖАЛА ПОВЕРХ КРУГОВ</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>у карточки был класс-модификатор .o, а .o в том же файле делает овалы абсолютно позиционированными. Модификатор переименован</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 3. Инфографика</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ЗНАК 知己 НЕ ОТОБРАЖАЛСЯ СОВСЕМ</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>подписи колец стояли по неверным координатам: полосы считались от высоты контейнера, а не от высоты овалов. Овалы увеличены до 440 x 360, позиции пересчитаны по фактическим полосам</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 4. Инфографика</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>подписи пересекали границы колец</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>русские пояснения сведены в одну строку с иероглифами, ширина проверена по хорде овала на нужной высоте</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 5. Инфографика</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>правая колонка разъезжалась</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ширины колонок зафиксированы: 296 + 440 + 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>ДЕФЕКТ 6. Инфографика</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>холст на 72 px больше содержимого</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>высота подобрана замером: 452 px при содержимом до 428</t>
         </is>
       </c>
     </row>

--- a/content/tz-drug-na-kitayskom.xlsx
+++ b/content/tz-drug-na-kitayskom.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ПЛАН 38 000–43 000. ФАКТ 44 128 — на 1 128 выше вилки, лимит 50 000 не нарушен</t>
+          <t>ПЛАН 38 000–43 000. ФАКТ 44 346 с адресами Tilda — на 1 346 выше вилки, лимит 50 000 не нарушен, запас 5 654</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>44 128 — НА 1 128 ВЫШЕ ВИЛКИ, лимит не нарушен, запас ≈ 5 800</t>
+          <t>44 346 с адресами Tilda — НА 1 346 ВЫШЕ ВИЛКИ, лимит не нарушен, запас 5 654</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>ждём ссылки от заказчика</t>
+          <t>7 / 5, assets = 0 — вшиты. ССЫЛКИ ПРИШЛИ В ОБРАТНОМ ПОРЯДКЕ: первой была инфографика (-kr.png), второй обложка. Вшивала по именам файлов, а не по порядку в сообщении</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com — подставляется после загрузки</t>
+          <t>https://static.tildacdn.com/tild6463-6539-4764-b938-383139376466/drug-na-kitayskom.png</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>адрес обложки на static.tildacdn.com</t>
+          <t>https://static.tildacdn.com/tild6463-6539-4764-b938-383139376466/drug-na-kitayskom.png</t>
         </is>
       </c>
     </row>
